--- a/sample.xlsx
+++ b/sample.xlsx
@@ -1,10 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
-  <workbookPr defaultThemeVersion="164011"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30326"/>
+  <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Universe\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{727B8AD8-07FD-4CFF-BBDA-6882B1F29009}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12645"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -18,12 +24,71 @@
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="16">
+  <si>
+    <t>question</t>
+  </si>
+  <si>
+    <t>option1</t>
+  </si>
+  <si>
+    <t>option2</t>
+  </si>
+  <si>
+    <t>option3</t>
+  </si>
+  <si>
+    <t>option4</t>
+  </si>
+  <si>
+    <t>answer</t>
+  </si>
+  <si>
+    <t>What is the capital of India?</t>
+  </si>
+  <si>
+    <t>Mumbai</t>
+  </si>
+  <si>
+    <t>New Delhi</t>
+  </si>
+  <si>
+    <t>Kolkata</t>
+  </si>
+  <si>
+    <t>Chennai</t>
+  </si>
+  <si>
+    <t>Which bank is the central bank of India?</t>
+  </si>
+  <si>
+    <t>SBI</t>
+  </si>
+  <si>
+    <t>HDFC</t>
+  </si>
+  <si>
+    <t>RBI</t>
+  </si>
+  <si>
+    <t>PNB</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="1" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="8"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -330,10 +395,72 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:F3"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <sheetData/>
+  <sheetData>
+    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E2" t="s">
+        <v>10</v>
+      </c>
+      <c r="F2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>11</v>
+      </c>
+      <c r="B3" t="s">
+        <v>12</v>
+      </c>
+      <c r="C3" t="s">
+        <v>13</v>
+      </c>
+      <c r="D3" t="s">
+        <v>14</v>
+      </c>
+      <c r="E3" t="s">
+        <v>15</v>
+      </c>
+      <c r="F3">
+        <v>2</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/sample.xlsx
+++ b/sample.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Universe\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{727B8AD8-07FD-4CFF-BBDA-6882B1F29009}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{29C0C722-38AA-45CC-8F4E-61808223A788}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="16">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11" uniqueCount="11">
   <si>
     <t>question</t>
   </si>
@@ -45,34 +45,19 @@
     <t>answer</t>
   </si>
   <si>
-    <t>What is the capital of India?</t>
-  </si>
-  <si>
-    <t>Mumbai</t>
-  </si>
-  <si>
-    <t>New Delhi</t>
-  </si>
-  <si>
-    <t>Kolkata</t>
-  </si>
-  <si>
-    <t>Chennai</t>
-  </si>
-  <si>
-    <t>Which bank is the central bank of India?</t>
-  </si>
-  <si>
-    <t>SBI</t>
-  </si>
-  <si>
-    <t>HDFC</t>
-  </si>
-  <si>
-    <t>RBI</t>
-  </si>
-  <si>
-    <t>PNB</t>
+    <t>Who is conventionally credited with inventing the telephone?</t>
+  </si>
+  <si>
+    <t>Thomas Edison</t>
+  </si>
+  <si>
+    <t>Alexander Graham Bell</t>
+  </si>
+  <si>
+    <t>Nikola Tesla</t>
+  </si>
+  <si>
+    <t>James Watt</t>
   </si>
 </sst>
 </file>
@@ -396,8 +381,11 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F3"/>
+  <dimension ref="A1:F2"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="57.42578125" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
@@ -437,26 +425,6 @@
       </c>
       <c r="F2">
         <v>1</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>11</v>
-      </c>
-      <c r="B3" t="s">
-        <v>12</v>
-      </c>
-      <c r="C3" t="s">
-        <v>13</v>
-      </c>
-      <c r="D3" t="s">
-        <v>14</v>
-      </c>
-      <c r="E3" t="s">
-        <v>15</v>
-      </c>
-      <c r="F3">
-        <v>2</v>
       </c>
     </row>
   </sheetData>

--- a/sample.xlsx
+++ b/sample.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Universe\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{29C0C722-38AA-45CC-8F4E-61808223A788}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{38F57C7D-ECF5-41FD-932A-537ED736619A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11" uniqueCount="11">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="33">
   <si>
     <t>question</t>
   </si>
@@ -45,19 +45,85 @@
     <t>answer</t>
   </si>
   <si>
-    <t>Who is conventionally credited with inventing the telephone?</t>
-  </si>
-  <si>
-    <t>Thomas Edison</t>
-  </si>
-  <si>
-    <t>Alexander Graham Bell</t>
-  </si>
-  <si>
-    <t>Nikola Tesla</t>
-  </si>
-  <si>
-    <t>James Watt</t>
+    <t>What does importing mean?</t>
+  </si>
+  <si>
+    <t>Which document is commonly used as evidence of the terms of a sea shipment and receipt of goods by a carrier?</t>
+  </si>
+  <si>
+    <t>Which institution in India is primarily responsible for regulating foreign trade under the Foreign Trade Policy?</t>
+  </si>
+  <si>
+    <t>What is a customs duty?</t>
+  </si>
+  <si>
+    <t>Which payment method commonly involves a bank undertaking to pay an exporter when compliant documents are presented under the agreed terms?</t>
+  </si>
+  <si>
+    <t>Which of the following documents may be used in an import transaction? Select every correct answer.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    Selling goods to another country</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    Commercial invoice</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    NITI Aayog</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    An insurance premium on cargo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    Open account</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    Transporting goods within one city</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    Packing list</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    Securities and Exchange Board of India (SEBI)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    A fee paid only to a shipping company</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    Consignment</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    Producing goods for domestic use only</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    Bill of lading</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    Reserve Bank of India (RBI)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    A tax or tariff imposed on goods crossing a customs border</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    Cash in advance</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    Buying goods or services from another country</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    Purchase requisition</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    Directorate General of Foreign Trade (DGFT)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    A discount offered by an exporter</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    Letter of credit</t>
+  </si>
+  <si>
+    <t>All of the above</t>
   </si>
 </sst>
 </file>
@@ -381,10 +447,11 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F2"/>
+  <dimension ref="A1:F7"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="57.42578125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="32.140625" customWidth="1"/>
+    <col min="5" max="5" width="44.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -412,19 +479,119 @@
         <v>6</v>
       </c>
       <c r="B2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C2" t="s">
+        <v>17</v>
+      </c>
+      <c r="D2" t="s">
+        <v>22</v>
+      </c>
+      <c r="E2" t="s">
+        <v>27</v>
+      </c>
+      <c r="F2">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
         <v>7</v>
       </c>
-      <c r="C2" t="s">
+      <c r="B3" t="s">
+        <v>13</v>
+      </c>
+      <c r="C3" t="s">
+        <v>18</v>
+      </c>
+      <c r="D3" t="s">
+        <v>23</v>
+      </c>
+      <c r="E3" t="s">
+        <v>28</v>
+      </c>
+      <c r="F3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
         <v>8</v>
       </c>
-      <c r="D2" t="s">
+      <c r="B4" t="s">
+        <v>14</v>
+      </c>
+      <c r="C4" t="s">
+        <v>19</v>
+      </c>
+      <c r="D4" t="s">
+        <v>24</v>
+      </c>
+      <c r="E4" t="s">
+        <v>29</v>
+      </c>
+      <c r="F4">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
         <v>9</v>
       </c>
-      <c r="E2" t="s">
+      <c r="B5" t="s">
+        <v>15</v>
+      </c>
+      <c r="C5" t="s">
+        <v>20</v>
+      </c>
+      <c r="D5" t="s">
+        <v>25</v>
+      </c>
+      <c r="E5" t="s">
+        <v>30</v>
+      </c>
+      <c r="F5">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
         <v>10</v>
       </c>
-      <c r="F2">
-        <v>1</v>
+      <c r="B6" t="s">
+        <v>16</v>
+      </c>
+      <c r="C6" t="s">
+        <v>21</v>
+      </c>
+      <c r="D6" t="s">
+        <v>26</v>
+      </c>
+      <c r="E6" t="s">
+        <v>31</v>
+      </c>
+      <c r="F6">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>11</v>
+      </c>
+      <c r="B7" t="s">
+        <v>18</v>
+      </c>
+      <c r="C7" t="s">
+        <v>13</v>
+      </c>
+      <c r="D7" t="s">
+        <v>23</v>
+      </c>
+      <c r="E7" t="s">
+        <v>32</v>
+      </c>
+      <c r="F7">
+        <v>3</v>
       </c>
     </row>
   </sheetData>

--- a/sample.xlsx
+++ b/sample.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Universe\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Competition\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{38F57C7D-ECF5-41FD-932A-537ED736619A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4833B9F2-3700-498E-BB9B-3C1F666AB1A7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="33">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="37" uniqueCount="34">
   <si>
     <t>question</t>
   </si>
@@ -124,6 +124,9 @@
   </si>
   <si>
     <t>All of the above</t>
+  </si>
+  <si>
+    <t>chapterId</t>
   </si>
 </sst>
 </file>
@@ -447,14 +450,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F7"/>
+  <dimension ref="A1:G7"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="32.140625" customWidth="1"/>
     <col min="5" max="5" width="44.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -473,8 +476,11 @@
       <c r="F1" t="s">
         <v>5</v>
       </c>
+      <c r="G1" t="s">
+        <v>33</v>
+      </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>6</v>
       </c>
@@ -494,7 +500,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>7</v>
       </c>
@@ -514,7 +520,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>8</v>
       </c>
@@ -534,7 +540,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>9</v>
       </c>
@@ -554,7 +560,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>10</v>
       </c>
@@ -574,7 +580,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>11</v>
       </c>
